--- a/daily/2026-04-01.xlsx
+++ b/daily/2026-04-01.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
         <bgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+        <bgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+        <bgColor rgb="0022C55E"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -66,6 +78,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1449,7 +1463,6 @@
       <c r="V12" t="n">
         <v>29</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
         <v>-14.6</v>
       </c>
@@ -2019,7 +2032,6 @@
       <c r="V19" t="n">
         <v>23</v>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
         <v>40.2</v>
       </c>
@@ -2097,7 +2109,6 @@
       <c r="V20" t="n">
         <v>11</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>18.1</v>
       </c>
@@ -2175,7 +2186,6 @@
       <c r="V21" t="n">
         <v>11</v>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
         <v>24</v>
       </c>
@@ -2499,7 +2509,6 @@
       <c r="V25" t="n">
         <v>23</v>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>5.7</v>
       </c>
@@ -3725,7 +3734,6 @@
       <c r="V40" t="n">
         <v>14</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>9.1</v>
       </c>
@@ -3967,7 +3975,6 @@
       <c r="V43" t="n">
         <v>14</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>13.1</v>
       </c>
@@ -4209,7 +4216,6 @@
       <c r="V46" t="n">
         <v>21</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>12.4</v>
       </c>
@@ -4369,7 +4375,6 @@
       <c r="V48" t="n">
         <v>21</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="n">
         <v>-48.6</v>
       </c>
@@ -4447,7 +4452,6 @@
       <c r="V49" t="n">
         <v>21</v>
       </c>
-      <c r="W49" t="inlineStr"/>
       <c r="X49" t="n">
         <v>0</v>
       </c>
@@ -4607,7 +4611,6 @@
       <c r="V51" t="n">
         <v>27</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="n">
         <v>-14.5</v>
       </c>
@@ -4685,7 +4688,6 @@
       <c r="V52" t="n">
         <v>27</v>
       </c>
-      <c r="W52" t="inlineStr"/>
       <c r="X52" t="n">
         <v>-13.5</v>
       </c>
@@ -4845,7 +4847,6 @@
       <c r="V54" t="n">
         <v>27</v>
       </c>
-      <c r="W54" t="inlineStr"/>
       <c r="X54" t="n">
         <v>2.8</v>
       </c>
@@ -5087,7 +5088,6 @@
       <c r="V57" t="n">
         <v>27</v>
       </c>
-      <c r="W57" t="inlineStr"/>
       <c r="X57" t="n">
         <v>12.7</v>
       </c>
@@ -5411,7 +5411,6 @@
       <c r="V61" t="n">
         <v>27</v>
       </c>
-      <c r="W61" t="inlineStr"/>
       <c r="X61" t="n">
         <v>0</v>
       </c>
@@ -5571,7 +5570,6 @@
       <c r="V63" t="n">
         <v>15</v>
       </c>
-      <c r="W63" t="inlineStr"/>
       <c r="X63" t="n">
         <v>-5</v>
       </c>
@@ -5731,7 +5729,6 @@
       <c r="V65" t="n">
         <v>15</v>
       </c>
-      <c r="W65" t="inlineStr"/>
       <c r="X65" t="n">
         <v>0</v>
       </c>
@@ -5809,7 +5806,6 @@
       <c r="V66" t="n">
         <v>15</v>
       </c>
-      <c r="W66" t="inlineStr"/>
       <c r="X66" t="n">
         <v>-32.6</v>
       </c>
@@ -5887,7 +5883,6 @@
       <c r="V67" t="n">
         <v>15</v>
       </c>
-      <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
         <v>3.5</v>
       </c>
@@ -5965,7 +5960,6 @@
       <c r="V68" t="n">
         <v>25</v>
       </c>
-      <c r="W68" t="inlineStr"/>
       <c r="X68" t="n">
         <v>-6.6</v>
       </c>
@@ -6207,7 +6201,6 @@
       <c r="V71" t="n">
         <v>25</v>
       </c>
-      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
         <v>0</v>
       </c>
@@ -6285,7 +6278,6 @@
       <c r="V72" t="n">
         <v>25</v>
       </c>
-      <c r="W72" t="inlineStr"/>
       <c r="X72" t="n">
         <v>-9</v>
       </c>
@@ -6363,7 +6355,6 @@
       <c r="V73" t="n">
         <v>25</v>
       </c>
-      <c r="W73" t="inlineStr"/>
       <c r="X73" t="n">
         <v>-12</v>
       </c>
@@ -6523,7 +6514,6 @@
       <c r="V75" t="n">
         <v>15</v>
       </c>
-      <c r="W75" t="inlineStr"/>
       <c r="X75" t="n">
         <v>-0.4</v>
       </c>
@@ -6601,7 +6591,6 @@
       <c r="V76" t="n">
         <v>1</v>
       </c>
-      <c r="W76" t="inlineStr"/>
       <c r="X76" t="n">
         <v>0</v>
       </c>
@@ -7007,7 +6996,6 @@
       <c r="V81" t="n">
         <v>1</v>
       </c>
-      <c r="W81" t="inlineStr"/>
       <c r="X81" t="n">
         <v>-24.2</v>
       </c>
@@ -7249,7 +7237,6 @@
       <c r="V84" t="n">
         <v>13</v>
       </c>
-      <c r="W84" t="inlineStr"/>
       <c r="X84" t="n">
         <v>9.4</v>
       </c>
@@ -8311,7 +8298,6 @@
       <c r="V97" t="n">
         <v>9</v>
       </c>
-      <c r="W97" t="inlineStr"/>
       <c r="X97" t="n">
         <v>11.5</v>
       </c>
@@ -8389,7 +8375,6 @@
       <c r="V98" t="n">
         <v>9</v>
       </c>
-      <c r="W98" t="inlineStr"/>
       <c r="X98" t="n">
         <v>3.8</v>
       </c>
@@ -8532,7 +8517,7 @@
         <v>50</v>
       </c>
       <c r="Q100" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>5.7</v>
@@ -8631,7 +8616,6 @@
       <c r="V101" t="n">
         <v>12</v>
       </c>
-      <c r="W101" t="inlineStr"/>
       <c r="X101" t="n">
         <v>11.7</v>
       </c>
@@ -14622,883 +14606,2027 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (11 pts vs 23.5 line, -12.5). Underperformed by 12.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: HR L10, FG Trend, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (18 pts vs 22.5 line, -4.5). Projection model called 18.9 pts — actual 18 was 0.9 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (14 pts vs 20.5 line, -6.5).</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E5" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (32 pts vs 18.5 line, +13.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (9 pts vs 18.5 line, -9.5).</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (7 pts vs 14.5 line, -7.5). Projection model called 8.7 pts — actual 7 was 1.7 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (16 pts vs 13.5 line, +2.5). Projection model targeted 12.1 pts (correct direction) but actual was 16. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, H2H.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (15 pts vs 11.5 line, +3.5). Projection model targeted 9.6 pts (correct direction) but actual was 15. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (14 pts vs 10.5 line, +3.5). Projection model (9.7 pts) and actual (14) both missed the mark. Key signals that disagreed: Volume, HR L30, HR L10. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (9 pts vs 10.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: FG Trend.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Jonathan Kuminga</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (12 pts vs 9.5 line, +2.5). Projection model targeted 3.3 pts (correct direction) but actual was 12. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Jock Landale</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (8 pts vs 7.5 line, +0.5). Projection model called 9.1 pts — actual 8 was 1.1 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Jevon Carter</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (3 pts vs 8.5 line, -5.5). Projection model targeted 11.3 pts (correct direction) but actual was 3. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>ATL @ ORL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (12 pts vs 11.5 line, +0.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (23 pts vs 15.5 line, +7.5). Projection model targeted 11.3 pts (correct direction) but actual was 23. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 12.5 line, -0.5). Projection model called 9.5 pts — actual 12 was 2.5 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (28 pts vs 28.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Will Riley</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (18 pts vs 14.5 line, +3.5). Projection model called 15.7 pts — actual 18 was 2.3 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (39 pts vs 18.5 line, +20.5). Overperformed by 20.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (6 pts vs 6.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Trend, H2H, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Adem Bona</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (13 pts vs 7.5 line, +5.5). Projection model targeted 3.4 pts (correct direction) but actual was 13. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Defense, Pace, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Quentin Grimes</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (12 pts vs 13.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Volume, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Bilal Coulibaly</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E24" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 12.5 line, -0.5).</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Tre Johnson</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (8 pts vs 12.5 line, -4.5). Projection model targeted 14.4 pts (correct direction) but actual was 8. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Tristan Vukcevic</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>PHI @ WAS</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E26" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (17 pts vs 12.5 line, +4.5).</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>23.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (25 pts vs 23.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, Context.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E28" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (13 pts vs 14.5 line, -1.5). Projection model called 12.3 pts — actual 13 was 0.7 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Davion Mitchell</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (21 pts vs 9.5 line, +11.5). Overperformed by 11.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: HR L10, H2H, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Baylor Scheierman</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (8 pts vs 5.5 line, +2.5). Projection model targeted 2.6 pts (correct direction) but actual was 8. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, Context.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Tyler Herro</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>23.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (18 pts vs 23.5 line, -5.5). Projection model called 18.0 pts — actual 18 was 0.0 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (16 pts vs 9.5 line, +6.5). Projection model targeted 8.2 pts (correct direction) but actual was 16. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, Trend, Pace.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (14 pts vs 16.5 line, -2.5). Projection model called 14.6 pts — actual 14 was 0.6 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (29 pts vs 20.5 line, +8.5).</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Derrick White</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 16.5 line, -10.5).</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (23 pts vs 7.5 line, +15.5).</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (43 pts vs 26.5 line, +16.5). Signal alignment was sound — 9/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Pelle Larsson</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (18 pts vs 11.5 line, +6.5). Projection model targeted 10.0 pts (correct direction) but actual was 18. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>BOS @ MIA</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E39" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (17 pts vs 13.5 line, +3.5). Projection model targeted 11.3 pts (correct direction) but actual was 17. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E40" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (27 pts vs 14.5 line, +12.5). Overperformed by 12.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, HR L30, Defense.</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (18 pts vs 14.5 line, +3.5). Projection model targeted 11.9 pts (correct direction) but actual was 18. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 14.5 line, -2.5). Projection model called 11.2 pts — actual 12 was 0.8 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>25.5</v>
       </c>
+      <c r="E43" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (19 pts vs 25.5 line, -6.5). Projection model targeted 27.8 pts (correct direction) but actual was 19. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E44" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (25 pts vs 18.5 line, +6.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>9.5</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (5 pts vs 9.5 line, -4.5). Projection model called 7.0 pts — actual 5 was 2.0 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -15520,245 +16648,569 @@
       <c r="D46" t="n">
         <v>20.5</v>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Gary Trent Jr.</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (0 pts vs 14.5 line, -14.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Ousmane Dieng</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E48" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (36 pts vs 12.5 line, +23.5). Overperformed by 23.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Trend, H2H, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Jericho Sims</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E49" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 6.5 line, -0.5). Signal alignment was sound — 9/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Clint Capela</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>MIL @ HOU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="E50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (2 pts vs 3.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E51" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (15 pts vs 13.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L10, Trend, H2H.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (20 pts vs 16.5 line, +3.5). Projection model targeted 11.3 pts (correct direction) but actual was 20. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (24 pts vs 14.5 line, +9.5).</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Cam Spencer</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E54" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (10 pts vs 9.5 line, +0.5). Projection model called 10.5 pts — actual 10 was 0.5 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (5 pts vs 14.5 line, -9.5). Projection model called 5.1 pts — actual 5 was 0.1 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (20 pts vs 21.5 line, -1.5).</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Walter Clayton Jr.</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E57" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (10 pts vs 7.5 line, +2.5). Projection model called 13.0 pts — actual 10 was 3.0 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>17.5</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (25 pts vs 17.5 line, +7.5). Projection model targeted 15.4 pts (correct direction) but actual was 25. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -15780,385 +17232,891 @@
       <c r="D59" t="n">
         <v>23.5</v>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Jordan Clarkson</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 10.5 line, -2.5). Projection model called 10.6 pts — actual 8 was 2.6 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>NYK @ MEM</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E61" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (17 pts vs 11.5 line, +5.5).</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>Precious Achiuwa</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E62" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (28 pts vs 12.5 line, +15.5).</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E63" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (20 pts vs 22.5 line, -2.5). Projection model called 22.2 pts — actual 20 was 2.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>DeMar DeRozan</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E64" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (28 pts vs 18.5 line, +9.5).</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Collin Murray-Boyles</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E65" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (20 pts vs 11.5 line, +8.5). Overperformed by 8.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E66" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 10.5 line, -2.5).</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E67" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (14 pts vs 18.5 line, -4.5). Projection model (19.0 pts) and actual (14) both missed the mark. Key signals that disagreed: Volume, HR L30, HR L10. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Maxime Raynaud</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 14.5 line, -8.5).</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>Malik Monk</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E69" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (18 pts vs 12.5 line, +5.5).</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Jamal Shead</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E70" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (16 pts vs 8.5 line, +7.5). Projection model targeted 4.7 pts (correct direction) but actual was 16. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Devin Carter</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E71" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (13 pts vs 12.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: HR L10, Trend, H2H.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>Dylan Cardwell</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E72" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (2 pts vs 5.5 line, -3.5). Projection model called 1.7 pts — actual 2 was 0.3 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Nique Clifford</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (9 pts vs 10.5 line, -1.5).</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Sandro Mamukelashvili</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E74" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (17 pts vs 13.5 line, +3.5). Projection model (13.3 pts) and actual (17) both missed the mark. Key signals that disagreed: HR L10, Trend, Defense. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>SAC @ TOR</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E75" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (18 pts vs 10.5 line, +7.5). Projection model targeted 8.3 pts (correct direction) but actual was 18. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L10, Defense.</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Kam Jones</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E76" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (9 pts vs 8.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Tre Jones</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E77" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (15 pts vs 16.5 line, -1.5). Projection model called 15.6 pts — actual 15 was 0.6 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="4" t="n">
         <v>24.5</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (25 pts vs 24.5 line, +0.5). Projection model called 25.4 pts — actual 25 was 0.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -16180,85 +18138,201 @@
       <c r="D79" t="n">
         <v>18.5</v>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Isaac Okoro</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E80" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (14 pts vs 10.5 line, +3.5). Projection model targeted 6.1 pts (correct direction) but actual was 14. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>Quenton Jackson</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E81" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 13.5 line, -5.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Collin Sexton</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E82" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (18 pts vs 18.5 line, -0.5).</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Matas Buzelis</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>IND @ CHI</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="4" t="n">
         <v>21.5</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (17 pts vs 21.5 line, -4.5). Projection model called 19.2 pts — actual 17 was 2.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -16280,385 +18354,891 @@
       <c r="D84" t="n">
         <v>10.5</v>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E85" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (15 pts vs 24.5 line, -9.5).</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Jamal Murray</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E86" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (37 pts vs 24.5 line, +12.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>Cameron Johnson</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E87" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (19 pts vs 11.5 line, +7.5). Signal alignment was sound — 9/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>Aaron Gordon</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E88" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 15.5 line, -9.5).</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>Cody Williams</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E89" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (9 pts vs 15.5 line, -6.5). Projection model called 11.6 pts — actual 9 was 2.6 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>Ace Bailey</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E90" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 19.5 line, -7.5).</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Tim Hardaway Jr.</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E91" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (3 pts vs 12.5 line, -9.5). Underperformed by 9.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: HR L10, Trend, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Bruce Brown</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E92" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (11 pts vs 7.5 line, +3.5). Projection model called 10.5 pts — actual 11 was 0.5 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Peyton Watson</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E93" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (6 pts vs 12.5 line, -6.5). Projection model targeted 15.2 pts (correct direction) but actual was 6. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, H2H, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Brice Sensabaugh</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E94" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (28 pts vs 21.5 line, +6.5). Projection model targeted 16.7 pts (correct direction) but actual was 28. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>Kyle Filipowski</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E95" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (25 pts vs 15.5 line, +9.5).</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>Christian Braun</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>DEN @ UTA</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E96" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (18 pts vs 11.5 line, +6.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>Will Richard</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E97" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (2 pts vs 9.5 line, -7.5). Projection model called 4.4 pts — actual 2 was 2.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Pat Spencer</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E98" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (14 pts vs 9.5 line, +4.5).</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>Victor Wembanyama</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E99" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (41 pts vs 25.5 line, +15.5).</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E100" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (11 pts vs 12.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Volume, HR L30, Defense.</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E101" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (13 pts vs 12.5 line, +0.5). Projection model called 14.5 pts — actual 13 was 1.5 off. Model accuracy strong on this play. Signal alignment was sound — 9/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E102" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (11 pts vs 16.5 line, -5.5).</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>Brandin Podziemski</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="4" t="n">
         <v>17.5</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (14 pts vs 17.5 line, -3.5). Projection model called 14.2 pts — actual 14 was 0.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -16680,85 +19260,201 @@
       <c r="D104" t="n">
         <v>16.5</v>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E105" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (15 pts vs 9.5 line, +5.5). Projection model targeted 8.3 pts (correct direction) but actual was 15. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>Draymond Green</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E106" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (14 pts vs 9.5 line, +4.5). Projection model targeted 8.5 pts (correct direction) but actual was 14. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E107" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (15 pts vs 16.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Volume, HR L30, Trend.</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>SAS @ GSW</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="4" t="n">
         <v>12.5</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 12.5 line, -4.5). Projection model called 8.9 pts — actual 8 was 0.9 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -16779,6 +19475,18 @@
       </c>
       <c r="D109" t="n">
         <v>12.5</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-04-02 07:30</t>
+        </is>
       </c>
     </row>
   </sheetData>
